--- a/examples/veneta/01_prices_veneta.xlsx
+++ b/examples/veneta/01_prices_veneta.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,7 +431,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Наименование товара</t>
+          <t>Наименование услуги</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -451,7 +451,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Картридж HP CF283A</t>
+          <t>Картридж HP CF283A (83A) для LaserJet M125/M127</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -469,7 +469,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Картридж Canon 725</t>
+          <t>Картридж HP CF258A (58A) для LaserJet M404/M428</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -478,7 +478,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3800</v>
+        <v>8200</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Картридж Brother TN-1075</t>
+          <t>Картридж HP CE285A (85A) для LaserJet P1102</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2200</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="7">
@@ -505,7 +505,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Тонер-картридж Samsung MLT-D101S</t>
+          <t>Картридж HP CF259X (59X) для LaserJet M404</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5100</v>
+        <v>9800</v>
       </c>
     </row>
     <row r="8">
@@ -523,7 +523,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Картридж Xerox 106R02773</t>
+          <t>Картридж HP CF410A (410A) Black</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>6300</v>
+        <v>7500</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Картридж Kyocera TK-1110</t>
+          <t>Картридж HP CF411A (410A) Cyan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2900</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="10">
@@ -559,7 +559,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Барабан HP CF234A</t>
+          <t>Картридж HP CF412A (410A) Yellow</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -569,6 +569,780 @@
       </c>
       <c r="D10" t="n">
         <v>7800</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Картридж HP CF413A (410A) Magenta</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Картридж HP Q2612A (12A) для LaserJet 1010</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Картридж HP CC388A (88A) для LaserJet P1007</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>3900</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Картридж Canon 725 для LBP6000</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Картридж Canon 728 для MF4410</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Картридж Canon 737 для MF211</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Картридж Canon 045 Black для LBP611</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Картридж Canon 052 для LBP212</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>7500</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Картридж Canon 057 для LBP223</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>8500</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Картридж Brother TN-1075 для HL-1110</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Картридж Brother TN-2080 для HL-2130</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Картридж Brother TN-2335 для HL-L2300</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>3400</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Картридж Brother TN-3480 для HL-L5000</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>5600</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Барабан Brother DR-1075 для HL-1110</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Барабан Brother DR-2335 для HL-L2300</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Тонер-картридж Samsung MLT-D101S для ML-2160</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>5100</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Тонер-картридж Samsung MLT-D111S для M2020</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>25</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Тонер-картридж Samsung MLT-D108S для ML-1640</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>4400</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>26</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Тонер-картридж Samsung MLT-D203L для M3320</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>8500</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>27</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Картридж Xerox 106R02773 для Phaser 3020</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>6300</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>28</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Картридж Xerox 106R03048 для Phaser 3020 (увелич.)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>29</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Картридж Xerox 106R02778 для WorkCentre 3215</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>30</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Картридж Xerox 113R00730 для Phaser 3200</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>5400</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>31</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Картридж Kyocera TK-1110 для FS-1040</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>2900</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>32</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Картридж Kyocera TK-1120 для FS-1060</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>3400</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>33</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Картридж Kyocera TK-1140 для FS-1035</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>5800</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>34</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Картридж Kyocera TK-1170 для M2040</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>35</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Тонер-картридж Epson C13S050709 для AcuLaser</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>5400</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>36</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Тонер-картридж Epson C13S050651 для M1400</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>37</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Картридж Lexmark 50F5H00 для MS310</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>38</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Картридж Lexmark 60F5H00 для MX310</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>39</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Барабан HP CF234A для LaserJet M106</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>40</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Барабан HP CF219A для LaserJet M104</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>6900</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>41</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Тонер для заправки Black 1кг (универсальный)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>42</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Тонер для заправки Cyan 1кг</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>43</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Тонер для заправки Yellow 1кг</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>44</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Тонер для заправки Magenta 1кг</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>45</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Чип для картриджа HP CF283A</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>46</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Чип для картриджа Samsung MLT-D101S</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>47</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Бумага офисная Снегурочка А4, 500 листов</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>пачка</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>48</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Бумага SvetoCopy A4, 500 листов</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>пачка</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>49</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Услуга заправки картриджа HP/Canon (стандарт)</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>50</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Услуга заправки картриджа цветного</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>1200</v>
       </c>
     </row>
   </sheetData>
